--- a/artfynd/A 27313-2024 artfynd.xlsx
+++ b/artfynd/A 27313-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110969439</v>
+        <v>110969443</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547760.0581326849</v>
+        <v>547785</v>
       </c>
       <c r="R2" t="n">
-        <v>7015311.232531754</v>
+        <v>7015427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110969437</v>
+        <v>110969445</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547798.4797371932</v>
+        <v>547798</v>
       </c>
       <c r="R3" t="n">
-        <v>7015274.872911638</v>
+        <v>7015420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110969440</v>
+        <v>110969439</v>
       </c>
       <c r="B4" t="n">
-        <v>96381</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547785.6345733423</v>
+        <v>547760</v>
       </c>
       <c r="R4" t="n">
-        <v>7015289.544278985</v>
+        <v>7015311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110969443</v>
+        <v>110969440</v>
       </c>
       <c r="B5" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547784.5049321693</v>
+        <v>547785</v>
       </c>
       <c r="R5" t="n">
-        <v>7015426.435049077</v>
+        <v>7015290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110969445</v>
+        <v>110969437</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547797.68679018</v>
+        <v>547799</v>
       </c>
       <c r="R6" t="n">
-        <v>7015419.425193521</v>
+        <v>7015275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 27313-2024 artfynd.xlsx
+++ b/artfynd/A 27313-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969437</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>